--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P46"/>
+  <dimension ref="A1:P54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2974,6 +2974,474 @@
         <v>4</v>
       </c>
     </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>BARRANQUILLA</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>CIUDAD DEL PARQUE TAYRONA APTOS</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>Germán Baquero</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Carlos Sandoval</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>CIUDAD DEL PARQUE</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t xml:space="preserve">JUEVES </t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr"/>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>4</v>
+      </c>
+      <c r="P47" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>BARRANQUILLA</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>DIMARO</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>José Luis Suarez</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Julio Curvelo </t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr"/>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr"/>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>MIERCOLES</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>2026-02-04, 2026-02-05, 2026-02-11, 2026-02-12, 2026-02-18, 2026-02-19, 2026-02-25, 2026-02-26</t>
+        </is>
+      </c>
+      <c r="O48" t="n">
+        <v>4</v>
+      </c>
+      <c r="P48" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>BARRANQUILLA</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>GENOVA</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>José Luis Suarez</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Erich Camargo</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr"/>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr"/>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr"/>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
+        <v>4</v>
+      </c>
+      <c r="P49" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>BARRANQUILLA</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>PARKSIDE</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>José Luis Suarez</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Ivan Barbosa</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr"/>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>LUNES</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>MARTES</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>2026-02-02, 2026-02-03, 2026-02-09, 2026-02-10, 2026-02-16, 2026-02-17, 2026-02-23, 2026-02-24</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>2026-02-03, 2026-02-04, 2026-02-10, 2026-02-11, 2026-02-17, 2026-02-18, 2026-02-24, 2026-02-25</t>
+        </is>
+      </c>
+      <c r="O50" t="n">
+        <v>4</v>
+      </c>
+      <c r="P50" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>BARRANQUILLA</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>PUERTA DORADA ARRECIFE</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>Germán Baquero</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Tatiana Navarro</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr"/>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr"/>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="O51" t="n">
+        <v>4</v>
+      </c>
+      <c r="P51" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>BARRANQUILLA</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>PUERTA DORADA MARISMA</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Germán Baquero</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Carlos Quiroz</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>SABADO</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="N52" t="inlineStr">
+        <is>
+          <t>2026-02-07, 2026-02-09, 2026-02-14, 2026-02-16, 2026-02-21, 2026-02-23, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="O52" t="n">
+        <v>4</v>
+      </c>
+      <c r="P52" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>BARRANQUILLA</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t xml:space="preserve">PUERTA DORADA NATURA </t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>Germán Baquero</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Lina Olarte</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr"/>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="N53" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="O53" t="n">
+        <v>4</v>
+      </c>
+      <c r="P53" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>BARRANQUILLA</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>RIVERBLUE</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Ejecución</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>José Luis Suarez</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Jeeniffer Perez</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr"/>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>JUEVES</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>VIERNES</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>2026-02-05, 2026-02-06, 2026-02-12, 2026-02-13, 2026-02-19, 2026-02-20, 2026-02-26, 2026-02-27</t>
+        </is>
+      </c>
+      <c r="N54" t="inlineStr">
+        <is>
+          <t>2026-02-06, 2026-02-07, 2026-02-13, 2026-02-14, 2026-02-20, 2026-02-21, 2026-02-27, 2026-02-28</t>
+        </is>
+      </c>
+      <c r="O54" t="n">
+        <v>4</v>
+      </c>
+      <c r="P54" t="n">
+        <v>4</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -3334,7 +3334,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t xml:space="preserve">PUERTA DORADA NATURA </t>
+          <t>PUERTA DORADA NATURA</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -2982,7 +2982,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CIUDAD DEL PARQUE TAYRONA APTOS</t>
+          <t>C DEL PARQUE TAYRONA APTOS</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">

--- a/output/calendario_teorico.xlsx
+++ b/output/calendario_teorico.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C12"/>
+  <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -436,7 +436,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PUERTA DORADA CRISTALINA</t>
+          <t>AMARETTO</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -446,150 +446,150 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AMARETTO</t>
+          <t>RIVERBAY</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RIVERBAY</t>
+          <t>C DEL PARQUE TAYRONA APTOS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C DEL PARQUE TAYRONA APTOS</t>
+          <t>DIMARO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>DIMARO</t>
+          <t>GENOVA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GENOVA</t>
+          <t>PARKSIDE</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-03-04, 2026-03-05, 2026-03-11, 2026-03-12, 2026-03-18, 2026-03-19, 2026-03-25, 2026-03-26</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PARKSIDE</t>
+          <t>PUERTA DORADA ARRECIFE</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>2026-03-02, 2026-03-03, 2026-03-09, 2026-03-10, 2026-03-16, 2026-03-17, 2026-03-24, 2026-03-25</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-03-03, 2026-03-04, 2026-03-10, 2026-03-11, 2026-03-17, 2026-03-18, 2026-03-24, 2026-03-25</t>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>PUERTA DORADA ARRECIFE</t>
+          <t>PUERTA DORADA MARISMA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-03-07, 2026-03-09, 2026-03-14, 2026-03-16, 2026-03-21, 2026-03-24, 2026-03-28</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>PUERTA DORADA MARISMA</t>
+          <t>PUERTA DORADA NATURA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+          <t>2026-03-05, 2026-03-06, 2026-03-12, 2026-03-13, 2026-03-19, 2026-03-20, 2026-03-26, 2026-03-27</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>2026-03-07, 2026-03-09, 2026-03-14, 2026-03-16, 2026-03-21, 2026-03-24, 2026-03-28</t>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>PUERTA DORADA NATURA</t>
+          <t>RIVERBLUE</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -606,7 +606,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>RIVERBLUE</t>
+          <t>PUERTA DORADA CRISTALINA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -615,6 +615,23 @@
         </is>
       </c>
       <c r="C12" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LOTE SEVILLA</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
         <is>
           <t>2026-03-06, 2026-03-07, 2026-03-13, 2026-03-14, 2026-03-20, 2026-03-21, 2026-03-27, 2026-03-28</t>
         </is>
